--- a/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
@@ -435,27 +435,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0321109180797046</v>
+        <v>0.03171112602109019</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03039812049158933</v>
+        <v>0.03121883407038753</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tendencia_media_meta</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03016388050157637</v>
+        <v>0.03111917373045871</v>
       </c>
     </row>
     <row r="5">
@@ -465,67 +465,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02978150274782522</v>
+        <v>0.02970445361751328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>meta_delta_1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02964291719987052</v>
+        <v>0.02904371861909031</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>meta_delta_media_4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02875693605458041</v>
+        <v>0.0283872405461161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02843604216852581</v>
+        <v>0.02764703361052735</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>meta_delta_media_4</t>
+          <t>tendencia_media_meta</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02780154153814535</v>
+        <v>0.02742081988303308</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meta_delta_1</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02759180440950932</v>
+        <v>0.02737416660205641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>meta_std_6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0270112330941064</v>
+        <v>0.02649439530366998</v>
       </c>
     </row>
     <row r="12">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02663137670220959</v>
+        <v>0.0263336676539837</v>
       </c>
     </row>
     <row r="13">
@@ -545,67 +545,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02639361488132305</v>
+        <v>0.02593948366137106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tendencia_curta_meta</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0255971489831002</v>
+        <v>0.02593303680532924</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>meta_std_6</t>
+          <t>meta_std_12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02526019625034303</v>
+        <v>0.02561186613603577</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>meta_lag_12</t>
+          <t>tendencia_curta_meta</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02479318773093839</v>
+        <v>0.02540159030530736</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta_std_12</t>
+          <t>meta_std_3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02451772824515535</v>
+        <v>0.02446345666183034</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>meta_std_3</t>
+          <t>meta_delta_2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02421877015267907</v>
+        <v>0.02309718174810584</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>meta_delta_2</t>
+          <t>meta_lag_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0232383183531454</v>
+        <v>0.02282902509161237</v>
       </c>
     </row>
     <row r="20">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02286982154550948</v>
+        <v>0.02234475132910033</v>
       </c>
     </row>
     <row r="21">
@@ -625,37 +625,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0224444815359298</v>
+        <v>0.02214091928422885</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meta_lag_6</t>
+          <t>meta_lag_12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02220487914289016</v>
+        <v>0.02203804016264587</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meta_lag_4</t>
+          <t>meta_media_6</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02081225316007125</v>
+        <v>0.0216109282863086</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta_media_6</t>
+          <t>meta_lag_4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02079464852783785</v>
+        <v>0.02077966528965165</v>
       </c>
     </row>
     <row r="25">
@@ -665,47 +665,47 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02064027722529169</v>
+        <v>0.019877161434729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta_media_4</t>
+          <t>meta_media_3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02044642369920131</v>
+        <v>0.01974382467407145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meta_lag_1</t>
+          <t>meta_lag_2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02008901341392209</v>
+        <v>0.01951288250267279</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta_media_3</t>
+          <t>meta_media_4</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01995814586373595</v>
+        <v>0.01937166513166851</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta_lag_2</t>
+          <t>meta_lag_1</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01985692790044084</v>
+        <v>0.01935751514886984</v>
       </c>
     </row>
     <row r="30">
@@ -715,87 +715,87 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01681124197560718</v>
+        <v>0.0193400652223201</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meta_max_12</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01647029673576027</v>
+        <v>0.01622595708177951</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meta_max_4</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01608059127717171</v>
+        <v>0.01621086759448179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meta_min_4</t>
+          <t>meta_max_12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01565798195143987</v>
+        <v>0.01614083446064899</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>meta_min_4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01561620220528208</v>
+        <v>0.01607811383587703</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>meta_min_12</t>
+          <t>meta_max_4</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01538555325567464</v>
+        <v>0.01590758866028507</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>meta_min_12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01454575688213252</v>
+        <v>0.01494324370201746</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>soma_alvo_12</t>
+          <t>media_alvo_12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01063394991591799</v>
+        <v>0.01068698302622509</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>media_alvo_12</t>
+          <t>soma_alvo_12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.01046034101854349</v>
+        <v>0.01043706392520726</v>
       </c>
     </row>
     <row r="39">
@@ -805,47 +805,47 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.009939390152442712</v>
+        <v>0.009288053125670312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hora_sin</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.009472511652929104</v>
+        <v>0.008800888453511653</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>soma_alvo_6</t>
+          <t>media_alvo_6</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.008967493506459963</v>
+        <v>0.008620094075324991</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>media_alvo_6</t>
+          <t>soma_alvo_6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.00883311212538679</v>
+        <v>0.008611710227378947</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dia_semana_sin</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.008638496222973514</v>
+        <v>0.008503230329846536</v>
       </c>
     </row>
     <row r="44">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.008393182127198279</v>
+        <v>0.008286483004831603</v>
       </c>
     </row>
     <row r="45">
@@ -865,17 +865,17 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.007875879084343148</v>
+        <v>0.007951634931266417</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>soma_alvo_3</t>
+          <t>media_alvo_3</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.007353355607513238</v>
+        <v>0.007271824731083957</v>
       </c>
     </row>
     <row r="47">
@@ -885,37 +885,37 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.007272074719309254</v>
+        <v>0.00721959465265075</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>media_alvo_3</t>
+          <t>soma_alvo_3</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.007250674038583309</v>
+        <v>0.00719707336708868</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tendencia_curta_1_3</t>
+          <t>tendencia_curta_1_6</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.006592574519707735</v>
+        <v>0.006872395794698227</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tendencia_curta_1_6</t>
+          <t>tendencia_curta_1_3</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.006577479469026849</v>
+        <v>0.006622975308318312</v>
       </c>
     </row>
     <row r="51">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.006446683737766738</v>
+        <v>0.006164444485088983</v>
       </c>
     </row>
     <row r="52">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.004638155625726879</v>
+        <v>0.005128705192894472</v>
       </c>
     </row>
     <row r="53">
@@ -945,77 +945,77 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.004378724514131436</v>
+        <v>0.004119266752419333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>alvo_lag_12</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.004272300633511655</v>
+        <v>0.004043870088688437</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>alvo_lag_1</t>
+          <t>alvo_lag_12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.004006795093193434</v>
+        <v>0.003891421993774294</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bloco_dia_cod</t>
+          <t>cluster_regime</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.003830724569932547</v>
+        <v>0.003814542173640201</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>alvo_lag_6</t>
+          <t>alvo_lag_1</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.003489520780313542</v>
+        <v>0.003804684985279956</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bloco_pico_manha</t>
+          <t>alvo_lag_6</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.003319119722158811</v>
+        <v>0.003470240605842224</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>alvo_lag_3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.00312395541752979</v>
+        <v>0.003356163447682831</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>alvo_lag_3</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.003086546987768972</v>
+        <v>0.002691616585106828</v>
       </c>
     </row>
     <row r="61">
@@ -1025,57 +1025,57 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.002572264841462873</v>
+        <v>0.002640681450833303</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>cluster_regime_3</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.002212668279533516</v>
+        <v>0.002640634949470266</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.001849465385290415</v>
+        <v>0.002414444662767475</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>eh_pico_manha</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.001721224398820794</v>
+        <v>0.002307195287700729</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.001662716703182259</v>
+        <v>0.001992958420668205</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.001625422735326023</v>
+        <v>0.00198896613495424</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.001615607556351353</v>
+        <v>0.001922938714768657</v>
       </c>
     </row>
     <row r="68">
@@ -1095,47 +1095,47 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.001540586468604823</v>
+        <v>0.001764879694784003</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.00150845221864333</v>
+        <v>0.001329057579355409</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cluster_regime</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.001311977964380138</v>
+        <v>0.001302342093034803</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mes_cos</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.001246860661876463</v>
+        <v>0.001301445819585189</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.001211979239888332</v>
+        <v>0.001248353973021758</v>
       </c>
     </row>
     <row r="73">
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.001104680781233131</v>
+        <v>0.001065648941837979</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.001037682787811505</v>
+        <v>0.001061021475294694</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cluster_regime_3</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0009894599552702022</v>
+        <v>0.001040130607185742</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>cluster_regime_2</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0008854325734970137</v>
+        <v>0.001018856346191557</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bloco_late_night</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0008328580938851788</v>
+        <v>0.0008415019289965765</v>
       </c>
     </row>
     <row r="78">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0007440933666608799</v>
+        <v>0.0008111638335411876</v>
       </c>
     </row>
     <row r="79">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0006549759038799428</v>
+        <v>0.0008077254702180891</v>
       </c>
     </row>
     <row r="80">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0006009592265264646</v>
+        <v>0.0007076561322176075</v>
       </c>
     </row>
     <row r="81">
@@ -1225,27 +1225,27 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0004652663333103259</v>
+        <v>0.0006644004675210052</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>bloco_madrugada</t>
+          <t>bloco_late_night</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0004259809207819468</v>
+        <v>0.0005185573714536146</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cluster_regime_2</t>
+          <t>bloco_madrugada</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0002966084791878907</v>
+        <v>0.0004001835122021606</v>
       </c>
     </row>
   </sheetData>

--- a/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,27 +435,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03171112602109019</v>
+        <v>0.1018775557368757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03121883407038753</v>
+        <v>0.08849698896767154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03111917373045871</v>
+        <v>0.08729513331279647</v>
       </c>
     </row>
     <row r="5">
@@ -465,787 +465,337 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02970445361751328</v>
+        <v>0.0860746079245608</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>meta_delta_1</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02904371861909031</v>
+        <v>0.08233926516403059</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meta_delta_media_4</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0283872405461161</v>
+        <v>0.0814181733173336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02764703361052735</v>
+        <v>0.07914773999701773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tendencia_media_meta</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02742081988303308</v>
+        <v>0.07684484976296418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02737416660205641</v>
+        <v>0.07627309979385208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>meta_std_6</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02649439530366998</v>
+        <v>0.04176814480003484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>meta_delta_media_12</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0263336676539837</v>
+        <v>0.03479547593589729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>meta_std_4</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02593948366137106</v>
+        <v>0.03454017574501737</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02593303680532924</v>
+        <v>0.02028075663717177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>meta_std_12</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02561186613603577</v>
+        <v>0.01965743402777784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tendencia_curta_meta</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02540159030530736</v>
+        <v>0.01554913913068216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta_std_3</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02446345666183034</v>
+        <v>0.01518253317338666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>meta_delta_2</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02309718174810584</v>
+        <v>0.005987691478636415</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>meta_lag_6</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02282902509161237</v>
+        <v>0.005332878651066517</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meta_delta_4</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02234475132910033</v>
+        <v>0.004847527865159116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>meta_media_12</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02214091928422885</v>
+        <v>0.00481748326797371</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meta_lag_12</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02203804016264587</v>
+        <v>0.004717407373338979</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meta_media_6</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0216109282863086</v>
+        <v>0.004175715592776643</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta_lag_4</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02077966528965165</v>
+        <v>0.004095873549951163</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta_lag_3</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.019877161434729</v>
+        <v>0.003801272483072811</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta_media_3</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01974382467407145</v>
+        <v>0.002397275198367447</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meta_lag_2</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01951288250267279</v>
+        <v>0.002322103470223671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta_media_4</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01937166513166851</v>
+        <v>0.002292181238587803</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta_lag_1</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01935751514886984</v>
+        <v>0.002235590102590565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0193400652223201</v>
+        <v>0.002133780512913754</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01622595708177951</v>
+        <v>0.001602870604829294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01621086759448179</v>
+        <v>0.001601602639811583</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meta_max_12</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01614083446064899</v>
+        <v>0.001595680794281525</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>meta_min_4</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01607811383587703</v>
+        <v>0.001469494071864175</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>meta_max_4</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01590758866028507</v>
+        <v>0.001171122382850351</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>meta_min_12</t>
+          <t>bloco_madrugada</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01494324370201746</v>
+        <v>0.001103735536364954</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>media_alvo_12</t>
+          <t>bloco_late_night</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01068698302622509</v>
+        <v>0.0007576397582689832</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>soma_alvo_12</t>
+          <t>bloco_outro</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.01043706392520726</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dia_semana</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.009288053125670312</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dia_semana_sin</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.008800888453511653</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>media_alvo_6</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.008620094075324991</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>soma_alvo_6</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.008611710227378947</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>hora_sin</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.008503230329846536</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>hora_cos</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.008286483004831603</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.007951634931266417</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>media_alvo_3</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.007271824731083957</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>dia_semana_cos</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.00721959465265075</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>soma_alvo_3</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.00719707336708868</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_6</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.006872395794698227</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_3</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.006622975308318312</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_2</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.006164444485088983</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>alvo_lag_2</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0.005128705192894472</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>alvo_lag_4</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0.004119266752419333</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>bloco_dia_cod</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.004043870088688437</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>alvo_lag_12</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0.003891421993774294</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cluster_regime</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.003814542173640201</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>alvo_lag_1</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.003804684985279956</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>alvo_lag_6</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.003470240605842224</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>alvo_lag_3</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.003356163447682831</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bloco_pico_manha</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.002691616585106828</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>acelerando_meta</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.002640681450833303</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cluster_regime_3</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.002640634949470266</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>eh_domingo</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.002414444662767475</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>chuva_mm</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.002307195287700729</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fim_semana</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.001992958420668205</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>eh_dia_util</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.00198896613495424</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>eh_sexta</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0.001922938714768657</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>eh_sabado</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.001764879694784003</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>eh_pico_manha</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.001329057579355409</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>estava_chovendo</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.001302342093034803</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>bloco_noite</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0.001301445819585189</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>bloco_tarde_pico</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0.001248353973021758</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>mes_sin</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0.001065648941837979</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0.001061021475294694</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>mes_cos</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0.001040130607185742</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cluster_regime_2</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.001018856346191557</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>bloco_manha</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0.0008415019289965765</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>bloco_almoco</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.0008111638335411876</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cluster_regime_1</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0.0008077254702180891</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>eh_pico_tarde</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.0007076561322176075</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>cluster_regime_0</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.0006644004675210052</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>bloco_late_night</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.0005185573714536146</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>bloco_madrugada</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.0004001835122021606</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
@@ -435,27 +435,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1018775557368757</v>
+        <v>0.1007477436386725</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08849698896767154</v>
+        <v>0.08768114142690267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08729513331279647</v>
+        <v>0.08735268299749666</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0860746079245608</v>
+        <v>0.08584721976818059</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08233926516403059</v>
+        <v>0.08418609371262928</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0814181733173336</v>
+        <v>0.08139998346486566</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07914773999701773</v>
+        <v>0.07867605743807055</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07684484976296418</v>
+        <v>0.07676221153144278</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07627309979385208</v>
+        <v>0.07585191828167918</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04176814480003484</v>
+        <v>0.0421649285117404</v>
       </c>
     </row>
     <row r="12">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03479547593589729</v>
+        <v>0.03649859104748954</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03454017574501737</v>
+        <v>0.03499642756608039</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02028075663717177</v>
+        <v>0.02029962459370157</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01965743402777784</v>
+        <v>0.01921162659037767</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01554913913068216</v>
+        <v>0.01536679143165392</v>
       </c>
     </row>
     <row r="17">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01518253317338666</v>
+        <v>0.01484839073805311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bloco_dia_cod</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.005987691478636415</v>
+        <v>0.005858624486073011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005332878651066517</v>
+        <v>0.005561771398461854</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.004847527865159116</v>
+        <v>0.005210075424430403</v>
       </c>
     </row>
     <row r="21">
@@ -625,47 +625,47 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00481748326797371</v>
+        <v>0.005047415661779265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bloco_pico_manha</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004717407373338979</v>
+        <v>0.004807565741088924</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>eh_sexta</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.004175715592776643</v>
+        <v>0.003833192640898511</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.004095873549951163</v>
+        <v>0.003827232011701447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eh_sabado</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003801272483072811</v>
+        <v>0.003707006532918553</v>
       </c>
     </row>
     <row r="26">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.002397275198367447</v>
+        <v>0.002441123606433572</v>
       </c>
     </row>
     <row r="27">
@@ -685,27 +685,27 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002322103470223671</v>
+        <v>0.002195338841170263</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002292181238587803</v>
+        <v>0.002129705812048925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002235590102590565</v>
+        <v>0.002035944474324061</v>
       </c>
     </row>
     <row r="30">
@@ -715,47 +715,47 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002133780512913754</v>
+        <v>0.002006685646440359</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>eh_pico_tarde</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001602870604829294</v>
+        <v>0.001773512683029283</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001601602639811583</v>
+        <v>0.001623167607980598</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001595680794281525</v>
+        <v>0.001574223569456558</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001469494071864175</v>
+        <v>0.001470732946706792</v>
       </c>
     </row>
     <row r="35">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001171122382850351</v>
+        <v>0.001119693462862993</v>
       </c>
     </row>
     <row r="36">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001103735536364954</v>
+        <v>0.001003483508732943</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0007576397582689832</v>
+        <v>0.0008820712044251726</v>
       </c>
     </row>
     <row r="38">

--- a/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1007477436386725</v>
+        <v>0.102411874362155</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08768114142690267</v>
+        <v>0.08866362931114513</v>
       </c>
     </row>
     <row r="4">
@@ -455,27 +455,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08735268299749666</v>
+        <v>0.08745169604462212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interacao_meta_umidade</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08584721976818059</v>
+        <v>0.08544933032137371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hora_sin</t>
+          <t>interacao_meta_umidade</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08418609371262928</v>
+        <v>0.08535145353304717</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08139998346486566</v>
+        <v>0.07931123248291888</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07867605743807055</v>
+        <v>0.07860570069389258</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07676221153144278</v>
+        <v>0.07675495362265027</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07585191828167918</v>
+        <v>0.07516689530990514</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0421649285117404</v>
+        <v>0.04207984779601039</v>
       </c>
     </row>
     <row r="12">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03649859104748954</v>
+        <v>0.03514007427550464</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03499642756608039</v>
+        <v>0.03467523883370825</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02029962459370157</v>
+        <v>0.02066856015948775</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01921162659037767</v>
+        <v>0.0198798909583532</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01536679143165392</v>
+        <v>0.01578856647674499</v>
       </c>
     </row>
     <row r="17">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01484839073805311</v>
+        <v>0.01490311537871762</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.005858624486073011</v>
+        <v>0.006672374882413985</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005561771398461854</v>
+        <v>0.005617050070041703</v>
       </c>
     </row>
     <row r="20">
@@ -615,37 +615,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005210075424430403</v>
+        <v>0.005123782667233184</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.005047415661779265</v>
+        <v>0.004750423730738455</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004807565741088924</v>
+        <v>0.004418122532479898</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003833192640898511</v>
+        <v>0.003772400977402587</v>
       </c>
     </row>
     <row r="24">
@@ -655,17 +655,17 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003827232011701447</v>
+        <v>0.003535829822411304</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eh_sexta</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003707006532918553</v>
+        <v>0.003426709181411787</v>
       </c>
     </row>
     <row r="26">
@@ -675,17 +675,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.002441123606433572</v>
+        <v>0.00288135926061918</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mes_cos</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002195338841170263</v>
+        <v>0.002087412107056779</v>
       </c>
     </row>
     <row r="28">
@@ -695,27 +695,27 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002129705812048925</v>
+        <v>0.002052398470533461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002035944474324061</v>
+        <v>0.001983009153225413</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002006685646440359</v>
+        <v>0.001973453134900552</v>
       </c>
     </row>
     <row r="31">
@@ -725,27 +725,27 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001773512683029283</v>
+        <v>0.001746192777624699</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001623167607980598</v>
+        <v>0.001571177016130707</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001574223569456558</v>
+        <v>0.001555771450906818</v>
       </c>
     </row>
     <row r="34">
@@ -755,27 +755,27 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001470732946706792</v>
+        <v>0.001514662942717419</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bloco_almoco</t>
+          <t>bloco_madrugada</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001119693462862993</v>
+        <v>0.001096953455663368</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bloco_madrugada</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001003483508732943</v>
+        <v>0.001010031204893732</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0008820712044251726</v>
+        <v>0.0009088256013580865</v>
       </c>
     </row>
     <row r="38">

--- a/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/rodovia_arao_sahm_km_95_braganca_paulista_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,370 +431,470 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>roll5_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.102411874362155</v>
+        <v>0.06892800668151323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>roll3_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08866362931114513</v>
+        <v>0.06032224686125208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08745169604462212</v>
+        <v>0.0577781884613393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hora_sin</t>
+          <t>lag1_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08544933032137371</v>
+        <v>0.05250465418764037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>interacao_meta_umidade</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08535145353304717</v>
+        <v>0.05087691239580189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07931123248291888</v>
+        <v>0.0482184722401682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hora_cos</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07860570069389258</v>
+        <v>0.04515234449511162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07675495362265027</v>
+        <v>0.04452962741368946</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07516689530990514</v>
+        <v>0.04225832031342452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04207984779601039</v>
+        <v>0.04197322588917738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>interacao_meta_umidade</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03514007427550464</v>
+        <v>0.04158991594190781</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>roll10_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03467523883370825</v>
+        <v>0.03983158243155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dia_semana</t>
+          <t>roll5_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02066856015948775</v>
+        <v>0.03741191589924452</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dia_semana_sin</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0198798909583532</v>
+        <v>0.03674785946170864</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dia_semana_cos</t>
+          <t>roll3_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01578856647674499</v>
+        <v>0.0363254841964969</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>lag1_pass_tendencia_5m</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01490311537871762</v>
+        <v>0.03463774378679076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bloco_pico_manha</t>
+          <t>lag1_pass_total_mercado</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.006672374882413985</v>
+        <v>0.03374843308125512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bloco_dia_cod</t>
+          <t>lag1_pass_media_ultimos_2min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005617050070041703</v>
+        <v>0.0287800655505976</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>lag1_pass_qtd_ultimos_2min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005123782667233184</v>
+        <v>0.02867452922304475</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004750423730738455</v>
+        <v>0.02854338504932729</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004418122532479898</v>
+        <v>0.02359340356974621</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>eh_sexta</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003772400977402587</v>
+        <v>0.02310968188165798</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eh_sabado</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003535829822411304</v>
+        <v>0.01444930925621905</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003426709181411787</v>
+        <v>0.0139948093137805</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eh_pico_manha</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00288135926061918</v>
+        <v>0.01204692278132481</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002087412107056779</v>
+        <v>0.01072849777285068</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002052398470533461</v>
+        <v>0.005892366642908525</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mes_cos</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001983009153225413</v>
+        <v>0.005161372271372274</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001973453134900552</v>
+        <v>0.003397128299896392</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001746192777624699</v>
+        <v>0.003203096584387764</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001571177016130707</v>
+        <v>0.003071603379090477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001555771450906818</v>
+        <v>0.002500977878106034</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>eh_pico_tarde</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001514662942717419</v>
+        <v>0.002444304953100562</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bloco_madrugada</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001096953455663368</v>
+        <v>0.002358414848851414</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bloco_almoco</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001010031204893732</v>
+        <v>0.00226120428562921</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bloco_late_night</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0009088256013580865</v>
+        <v>0.001658563872001097</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>bloco_noite</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.001560964141333729</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bloco_tarde_pico</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.001408376658303154</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>estava_chovendo</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.001321723175681719</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eh_pico_tarde</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.001238316534621639</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mes_sin</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.001182883546399151</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.001143647359430025</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mes_cos</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.001102415547185031</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bloco_almoco</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0008785474719550688</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bloco_late_night</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0007313525717955814</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bloco_madrugada</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0007272018413303088</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>bloco_outro</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B48" t="n">
         <v>0</v>
       </c>
     </row>
